--- a/reports/Debug-snowbowl-20251230/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/Month to Date (Prior Year)_Visits.xlsx
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45628</v>
+        <v>45627</v>
       </c>
       <c r="C33" s="2">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>45629</v>
       </c>
       <c r="C34" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,13 +893,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C35" s="2">
-        <v>384</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,10 +907,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="C36" s="2">
-        <v>893</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -921,13 +921,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="C37" s="2">
-        <v>711</v>
+        <v>65</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="C38" s="2">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -949,13 +949,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C39" s="2">
-        <v>504</v>
+        <v>49</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C40" s="2">
-        <v>735</v>
+        <v>56</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,13 +977,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45636</v>
+        <v>45641</v>
       </c>
       <c r="C41" s="2">
-        <v>63</v>
+        <v>1165</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45638</v>
+        <v>45642</v>
       </c>
       <c r="C42" s="2">
-        <v>714</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1005,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
       <c r="C43" s="2">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45641</v>
+        <v>45644</v>
       </c>
       <c r="C44" s="2">
-        <v>3</v>
+        <v>1245</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45642</v>
+        <v>45645</v>
       </c>
       <c r="C45" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45644</v>
+        <v>45646</v>
       </c>
       <c r="C46" s="2">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1061,10 +1061,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45644</v>
+        <v>45646</v>
       </c>
       <c r="C47" s="2">
-        <v>70</v>
+        <v>929</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1075,10 +1075,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45645</v>
+        <v>45647</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>45647</v>
       </c>
       <c r="C49" s="2">
-        <v>98</v>
+        <v>1531</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>45648</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>45648</v>
       </c>
       <c r="C51" s="2">
-        <v>9</v>
+        <v>224</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45650</v>
+        <v>45649</v>
       </c>
       <c r="C52" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C53" s="2">
-        <v>532</v>
+        <v>1051</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C54" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1173,13 +1173,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45653</v>
+        <v>45650</v>
       </c>
       <c r="C55" s="2">
-        <v>52</v>
+        <v>1443</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45654</v>
+        <v>45651</v>
       </c>
       <c r="C56" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,10 +1201,10 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45655</v>
+        <v>45651</v>
       </c>
       <c r="C57" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
@@ -1215,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45628</v>
+        <v>45652</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>837</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1229,10 +1229,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45628</v>
+        <v>45653</v>
       </c>
       <c r="C59" s="2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1243,10 +1243,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45629</v>
+        <v>45654</v>
       </c>
       <c r="C60" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1257,10 +1257,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45631</v>
+        <v>45655</v>
       </c>
       <c r="C61" s="2">
-        <v>2</v>
+        <v>646</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45631</v>
+        <v>45656</v>
       </c>
       <c r="C62" s="2">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1285,10 +1285,10 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45634</v>
+        <v>45656</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1299,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C64" s="2">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1313,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45635</v>
+        <v>45628</v>
       </c>
       <c r="C65" s="2">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1327,10 +1327,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C66" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1341,10 +1341,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45637</v>
+        <v>45631</v>
       </c>
       <c r="C67" s="2">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1355,13 +1355,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45638</v>
+        <v>45631</v>
       </c>
       <c r="C68" s="2">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1369,10 +1369,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45639</v>
+        <v>45634</v>
       </c>
       <c r="C69" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1383,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45641</v>
+        <v>45634</v>
       </c>
       <c r="C70" s="2">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45642</v>
+        <v>45635</v>
       </c>
       <c r="C71" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45642</v>
+        <v>45636</v>
       </c>
       <c r="C72" s="2">
-        <v>602</v>
+        <v>6</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1425,13 +1425,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45644</v>
+        <v>45637</v>
       </c>
       <c r="C73" s="2">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1439,13 +1439,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="C74" s="2">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1453,10 +1453,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45645</v>
+        <v>45639</v>
       </c>
       <c r="C75" s="2">
-        <v>607</v>
+        <v>7</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1467,13 +1467,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45645</v>
+        <v>45641</v>
       </c>
       <c r="C76" s="2">
-        <v>1230</v>
+        <v>98</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1481,10 +1481,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45648</v>
+        <v>45642</v>
       </c>
       <c r="C77" s="2">
-        <v>903</v>
+        <v>6</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1495,13 +1495,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45648</v>
+        <v>45642</v>
       </c>
       <c r="C78" s="2">
-        <v>1613</v>
+        <v>602</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,13 +1509,13 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45649</v>
+        <v>45644</v>
       </c>
       <c r="C79" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45650</v>
+        <v>45645</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1537,10 +1537,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45651</v>
+        <v>45645</v>
       </c>
       <c r="C81" s="2">
-        <v>2</v>
+        <v>607</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1551,13 +1551,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45651</v>
+        <v>45645</v>
       </c>
       <c r="C82" s="2">
-        <v>830</v>
+        <v>1230</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,13 +1565,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45651</v>
+        <v>45648</v>
       </c>
       <c r="C83" s="2">
-        <v>1321</v>
+        <v>903</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45652</v>
+        <v>45648</v>
       </c>
       <c r="C84" s="2">
-        <v>384</v>
+        <v>1613</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45654</v>
+        <v>45649</v>
       </c>
       <c r="C85" s="2">
-        <v>4</v>
+        <v>241</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1607,13 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45654</v>
+        <v>45650</v>
       </c>
       <c r="C86" s="2">
-        <v>1825</v>
+        <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45655</v>
+        <v>45651</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1635,13 +1635,13 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45655</v>
+        <v>45651</v>
       </c>
       <c r="C88" s="2">
-        <v>493</v>
+        <v>830</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1649,13 +1649,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45627</v>
+        <v>45651</v>
       </c>
       <c r="C89" s="2">
-        <v>61</v>
+        <v>1321</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1663,13 +1663,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45628</v>
+        <v>45652</v>
       </c>
       <c r="C90" s="2">
-        <v>6</v>
+        <v>384</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1677,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45628</v>
+        <v>45654</v>
       </c>
       <c r="C91" s="2">
-        <v>476</v>
+        <v>4</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1691,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>45629</v>
+        <v>45654</v>
       </c>
       <c r="C92" s="2">
-        <v>29</v>
+        <v>1825</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,10 +1705,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>45630</v>
+        <v>45655</v>
       </c>
       <c r="C93" s="2">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1719,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>45630</v>
+        <v>45655</v>
       </c>
       <c r="C94" s="2">
-        <v>416</v>
+        <v>493</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1733,13 +1733,13 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C95" s="2">
-        <v>383</v>
+        <v>637</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1747,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C96" s="2">
+        <v>53</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C97" s="2">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,10 +1775,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C98" s="2">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1789,13 +1789,13 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C99" s="2">
-        <v>881</v>
+        <v>93</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1803,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>45634</v>
+        <v>45636</v>
       </c>
       <c r="C100" s="2">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1817,13 +1817,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>45634</v>
+        <v>45637</v>
       </c>
       <c r="C101" s="2">
-        <v>945</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1831,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C102" s="2">
-        <v>5</v>
+        <v>778</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,10 +1845,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C103" s="2">
-        <v>338</v>
+        <v>51</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1859,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C104" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,10 +1873,10 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C105" s="2">
-        <v>816</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1890,10 +1890,10 @@
         <v>45640</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>1649</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,10 +1901,10 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>45640</v>
+        <v>45642</v>
       </c>
       <c r="C107" s="2">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>5</v>
@@ -1915,13 +1915,13 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>45641</v>
+        <v>45643</v>
       </c>
       <c r="C108" s="2">
-        <v>13</v>
+        <v>1155</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1929,13 +1929,13 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>45641</v>
+        <v>45643</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,13 +1943,13 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="C110" s="2">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1957,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>45647</v>
+        <v>45645</v>
       </c>
       <c r="C111" s="2">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>5</v>
@@ -1971,10 +1971,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="C112" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1985,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C113" s="2">
-        <v>279</v>
+        <v>936</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1999,13 +1999,13 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>45650</v>
+        <v>45646</v>
       </c>
       <c r="C114" s="2">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2013,10 +2013,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>45651</v>
+        <v>45647</v>
       </c>
       <c r="C115" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2027,13 +2027,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C116" s="2">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>45653</v>
+        <v>45649</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2055,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>45654</v>
+        <v>45650</v>
       </c>
       <c r="C118" s="2">
-        <v>455</v>
+        <v>16</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2069,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>45655</v>
+        <v>45650</v>
       </c>
       <c r="C119" s="2">
-        <v>333</v>
+        <v>766</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,10 +2083,10 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>45656</v>
+        <v>45652</v>
       </c>
       <c r="C120" s="2">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>5</v>
@@ -2097,13 +2097,13 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>45627</v>
+        <v>45652</v>
       </c>
       <c r="C121" s="2">
-        <v>786</v>
+        <v>8</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,13 +2111,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>45627</v>
+        <v>45653</v>
       </c>
       <c r="C122" s="2">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>45628</v>
+        <v>45653</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>533</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2139,10 +2139,10 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>45629</v>
+        <v>45656</v>
       </c>
       <c r="C124" s="2">
-        <v>40</v>
+        <v>633</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2153,13 +2153,13 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C125" s="2">
-        <v>485</v>
+        <v>61</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2167,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C126" s="2">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C127" s="2">
-        <v>4</v>
+        <v>476</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2195,13 +2195,13 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>45633</v>
+        <v>45629</v>
       </c>
       <c r="C128" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2209,13 +2209,13 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C129" s="2">
-        <v>1404</v>
+        <v>51</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2223,13 +2223,13 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C130" s="2">
-        <v>118</v>
+        <v>416</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2237,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C131" s="2">
-        <v>10</v>
+        <v>383</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2251,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C132" s="2">
-        <v>854</v>
+        <v>7</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>5</v>
@@ -2265,13 +2265,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>45636</v>
+        <v>45632</v>
       </c>
       <c r="C133" s="2">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2279,13 +2279,13 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C134" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C135" s="2">
-        <v>2</v>
+        <v>881</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -2307,10 +2307,10 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>45637</v>
+        <v>45634</v>
       </c>
       <c r="C136" s="2">
-        <v>535</v>
+        <v>2</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2321,13 +2321,13 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>45640</v>
+        <v>45634</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>945</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2335,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C138" s="2">
-        <v>829</v>
+        <v>5</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,10 +2349,10 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C139" s="2">
-        <v>2</v>
+        <v>338</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>5</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C140" s="2">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2377,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>45643</v>
+        <v>45639</v>
       </c>
       <c r="C141" s="2">
-        <v>523</v>
+        <v>816</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2391,13 +2391,13 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>45644</v>
+        <v>45640</v>
       </c>
       <c r="C142" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2405,10 +2405,10 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>45647</v>
+        <v>45640</v>
       </c>
       <c r="C143" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2419,10 +2419,10 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>45647</v>
+        <v>45641</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>45647</v>
+        <v>45641</v>
       </c>
       <c r="C145" s="2">
-        <v>254</v>
+        <v>1</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2447,13 +2447,13 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>45648</v>
+        <v>45645</v>
       </c>
       <c r="C146" s="2">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2461,10 +2461,10 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>45650</v>
+        <v>45647</v>
       </c>
       <c r="C147" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2475,10 +2475,10 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>45650</v>
+        <v>45647</v>
       </c>
       <c r="C148" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>5</v>
@@ -2489,10 +2489,10 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>45650</v>
+        <v>45648</v>
       </c>
       <c r="C149" s="2">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>7</v>
@@ -2503,10 +2503,10 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C150" s="2">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>5</v>
@@ -2517,13 +2517,13 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>45653</v>
+        <v>45651</v>
       </c>
       <c r="C151" s="2">
-        <v>1776</v>
+        <v>4</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,13 +2531,13 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>45655</v>
+        <v>45651</v>
       </c>
       <c r="C152" s="2">
-        <v>58</v>
+        <v>288</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2545,13 +2545,13 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C153" s="2">
-        <v>1705</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2559,13 +2559,13 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>45627</v>
+        <v>45654</v>
       </c>
       <c r="C154" s="2">
-        <v>3</v>
+        <v>455</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,13 +2573,13 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>45627</v>
+        <v>45655</v>
       </c>
       <c r="C155" s="2">
-        <v>109</v>
+        <v>333</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2587,10 +2587,10 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>45629</v>
+        <v>45656</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2601,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C157" s="2">
-        <v>455</v>
+        <v>786</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>6</v>
@@ -2615,13 +2615,13 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C159" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2643,13 +2643,13 @@
         <v>1</v>
       </c>
       <c r="B160" s="2">
-        <v>45631</v>
+        <v>45629</v>
       </c>
       <c r="C160" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2657,13 +2657,13 @@
         <v>1</v>
       </c>
       <c r="B161" s="2">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C161" s="2">
-        <v>68</v>
+        <v>485</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="B162" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C162" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2685,13 +2685,13 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C163" s="2">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2699,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C164" s="2">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>5</v>
@@ -2713,13 +2713,13 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C165" s="2">
-        <v>4</v>
+        <v>1404</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2727,10 +2727,10 @@
         <v>1</v>
       </c>
       <c r="B166" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C166" s="2">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>8</v>
@@ -2741,10 +2741,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C167" s="2">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>5</v>
@@ -2755,10 +2755,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C168" s="2">
-        <v>514</v>
+        <v>854</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2769,10 +2769,10 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C169" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>5</v>
@@ -2783,10 +2783,10 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C170" s="2">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>8</v>
@@ -2797,10 +2797,10 @@
         <v>1</v>
       </c>
       <c r="B171" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C171" s="2">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2811,10 +2811,10 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C172" s="2">
-        <v>802</v>
+        <v>535</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>5</v>
@@ -2825,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="B173" s="2">
-        <v>45643</v>
+        <v>45640</v>
       </c>
       <c r="C173" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>5</v>
@@ -2839,10 +2839,10 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>45644</v>
+        <v>45640</v>
       </c>
       <c r="C174" s="2">
-        <v>547</v>
+        <v>829</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>5</v>
@@ -2853,10 +2853,10 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>45646</v>
+        <v>45641</v>
       </c>
       <c r="C175" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2867,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>45646</v>
+        <v>45641</v>
       </c>
       <c r="C176" s="2">
-        <v>2</v>
+        <v>155</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2881,10 +2881,10 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>45647</v>
+        <v>45643</v>
       </c>
       <c r="C177" s="2">
-        <v>890</v>
+        <v>523</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2895,13 +2895,13 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>45649</v>
+        <v>45644</v>
       </c>
       <c r="C178" s="2">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="2">
-        <v>45649</v>
+        <v>45647</v>
       </c>
       <c r="C179" s="2">
-        <v>1266</v>
+        <v>3</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2923,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>45649</v>
+        <v>45647</v>
       </c>
       <c r="C180" s="2">
         <v>1</v>
@@ -2937,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>45652</v>
+        <v>45647</v>
       </c>
       <c r="C181" s="2">
-        <v>1873</v>
+        <v>254</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2951,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="B182" s="2">
-        <v>45653</v>
+        <v>45648</v>
       </c>
       <c r="C182" s="2">
-        <v>455</v>
+        <v>5</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2965,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>45655</v>
+        <v>45650</v>
       </c>
       <c r="C183" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2979,13 +2979,13 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>45655</v>
+        <v>45650</v>
       </c>
       <c r="C184" s="2">
-        <v>1575</v>
+        <v>6</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2993,10 +2993,10 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>45656</v>
+        <v>45650</v>
       </c>
       <c r="C185" s="2">
-        <v>546</v>
+        <v>316</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>7</v>
@@ -3007,10 +3007,10 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>45627</v>
+        <v>45652</v>
       </c>
       <c r="C186" s="2">
-        <v>637</v>
+        <v>31</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>5</v>
@@ -3021,13 +3021,13 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>45628</v>
+        <v>45653</v>
       </c>
       <c r="C187" s="2">
-        <v>53</v>
+        <v>1776</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3035,13 +3035,13 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>45631</v>
+        <v>45655</v>
       </c>
       <c r="C188" s="2">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3049,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>45634</v>
+        <v>45656</v>
       </c>
       <c r="C189" s="2">
-        <v>2</v>
+        <v>1705</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3063,13 +3063,13 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C190" s="2">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3077,10 +3077,10 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>45636</v>
+        <v>45629</v>
       </c>
       <c r="C191" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3091,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>45637</v>
+        <v>45629</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3105,13 +3105,13 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>45637</v>
+        <v>45632</v>
       </c>
       <c r="C193" s="2">
-        <v>778</v>
+        <v>893</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3119,13 +3119,13 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>45639</v>
+        <v>45632</v>
       </c>
       <c r="C194" s="2">
-        <v>51</v>
+        <v>711</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,13 +3133,13 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>45640</v>
+        <v>45633</v>
       </c>
       <c r="C195" s="2">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3147,10 +3147,10 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C196" s="2">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3161,10 +3161,10 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C197" s="2">
-        <v>1649</v>
+        <v>735</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>6</v>
@@ -3175,13 +3175,13 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>45642</v>
+        <v>45636</v>
       </c>
       <c r="C198" s="2">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>45643</v>
+        <v>45638</v>
       </c>
       <c r="C199" s="2">
-        <v>1155</v>
+        <v>714</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>6</v>
@@ -3203,13 +3203,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>45643</v>
+        <v>45639</v>
       </c>
       <c r="C200" s="2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,10 +3217,10 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>45644</v>
+        <v>45641</v>
       </c>
       <c r="C201" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3231,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>45645</v>
+        <v>45642</v>
       </c>
       <c r="C202" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3245,10 +3245,10 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C203" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3259,13 +3259,13 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C204" s="2">
-        <v>936</v>
+        <v>70</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C205" s="2">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>45647</v>
       </c>
       <c r="C206" s="2">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>5</v>
@@ -3301,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C207" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>5</v>
@@ -3315,13 +3315,13 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C208" s="2">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>45650</v>
       </c>
       <c r="C209" s="2">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>5</v>
@@ -3343,13 +3343,13 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="C210" s="2">
-        <v>766</v>
+        <v>532</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>45652</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>5</v>
@@ -3371,13 +3371,13 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="C212" s="2">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3385,13 +3385,13 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="C213" s="2">
-        <v>6</v>
+        <v>239</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3399,10 +3399,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>45653</v>
+        <v>45655</v>
       </c>
       <c r="C214" s="2">
-        <v>533</v>
+        <v>5</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>5</v>
@@ -3413,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>45656</v>
+        <v>45627</v>
       </c>
       <c r="C215" s="2">
-        <v>633</v>
+        <v>3</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3430,10 +3430,10 @@
         <v>45627</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3444,10 +3444,10 @@
         <v>45629</v>
       </c>
       <c r="C217" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3455,13 +3455,13 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C218" s="2">
-        <v>60</v>
+        <v>455</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3469,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>45635</v>
+        <v>45630</v>
       </c>
       <c r="C219" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3483,10 +3483,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>45635</v>
+        <v>45630</v>
       </c>
       <c r="C220" s="2">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>7</v>
@@ -3497,13 +3497,13 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>45638</v>
+        <v>45631</v>
       </c>
       <c r="C221" s="2">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3511,13 +3511,13 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>45639</v>
+        <v>45632</v>
       </c>
       <c r="C222" s="2">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="2">
-        <v>45640</v>
+        <v>45633</v>
       </c>
       <c r="C223" s="2">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3539,13 +3539,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>45641</v>
+        <v>45634</v>
       </c>
       <c r="C224" s="2">
-        <v>1165</v>
+        <v>108</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3553,13 +3553,13 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>45642</v>
+        <v>45635</v>
       </c>
       <c r="C225" s="2">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3567,10 +3567,10 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>45643</v>
+        <v>45636</v>
       </c>
       <c r="C226" s="2">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3581,13 +3581,13 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>45644</v>
+        <v>45637</v>
       </c>
       <c r="C227" s="2">
-        <v>1245</v>
+        <v>28</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3595,13 +3595,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="C228" s="2">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3609,10 +3609,10 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>45646</v>
+        <v>45638</v>
       </c>
       <c r="C229" s="2">
-        <v>78</v>
+        <v>514</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3623,10 +3623,10 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>45646</v>
+        <v>45640</v>
       </c>
       <c r="C230" s="2">
-        <v>929</v>
+        <v>9</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>5</v>
@@ -3637,13 +3637,13 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>45647</v>
+        <v>45640</v>
       </c>
       <c r="C231" s="2">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,13 +3651,13 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>45647</v>
+        <v>45641</v>
       </c>
       <c r="C232" s="2">
-        <v>1531</v>
+        <v>74</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3665,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>45648</v>
+        <v>45641</v>
       </c>
       <c r="C233" s="2">
-        <v>16</v>
+        <v>802</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3679,13 +3679,13 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>45648</v>
+        <v>45643</v>
       </c>
       <c r="C234" s="2">
-        <v>224</v>
+        <v>8</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3693,10 +3693,10 @@
         <v>1</v>
       </c>
       <c r="B235" s="2">
-        <v>45649</v>
+        <v>45644</v>
       </c>
       <c r="C235" s="2">
-        <v>57</v>
+        <v>547</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>5</v>
@@ -3707,10 +3707,10 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>45649</v>
+        <v>45646</v>
       </c>
       <c r="C236" s="2">
-        <v>1051</v>
+        <v>7</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>5</v>
@@ -3721,10 +3721,10 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>45650</v>
+        <v>45646</v>
       </c>
       <c r="C237" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>5</v>
@@ -3735,13 +3735,13 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>45650</v>
+        <v>45647</v>
       </c>
       <c r="C238" s="2">
-        <v>1443</v>
+        <v>890</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3749,10 +3749,10 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C239" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3763,13 +3763,13 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C240" s="2">
-        <v>1</v>
+        <v>1266</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3777,10 +3777,10 @@
         <v>1</v>
       </c>
       <c r="B241" s="2">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="C241" s="2">
-        <v>837</v>
+        <v>1</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>5</v>
@@ -3791,13 +3791,13 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>45653</v>
+        <v>45652</v>
       </c>
       <c r="C242" s="2">
-        <v>1</v>
+        <v>1873</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3805,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>45654</v>
+        <v>45653</v>
       </c>
       <c r="C243" s="2">
-        <v>13</v>
+        <v>455</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>45655</v>
       </c>
       <c r="C244" s="2">
-        <v>646</v>
+        <v>7</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3833,13 +3833,13 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>45656</v>
+        <v>45655</v>
       </c>
       <c r="C245" s="2">
-        <v>7</v>
+        <v>1575</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3850,10 +3850,10 @@
         <v>45656</v>
       </c>
       <c r="C246" s="2">
-        <v>2</v>
+        <v>546</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
